--- a/agentic-qe-mvp/demo-artifacts/flow-2-incremental-CYC-5/09-report/CYC-5-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-incremental-CYC-5/09-report/CYC-5-cycle-report.xlsx
@@ -172,7 +172,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807) at 2026-10-02T03:54:17.817Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807) at 2026-10-02T04:13:56.665Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1080,7 +1080,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T03:54:19.333Z</t>
+    <t>2026-10-02T04:13:58.150Z</t>
   </si>
   <si>
     <t>14 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -1092,7 +1092,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-02T03:54:19.347Z</t>
+    <t>2026-10-02T04:13:58.167Z</t>
   </si>
   <si>
     <t>4 requirements, 5 test cases, 4 scripts merged: BL-4 v1 -&gt; v2</t>
@@ -3827,7 +3827,7 @@
         <v>268</v>
       </c>
       <c r="E3" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -3845,7 +3845,7 @@
         <v>268</v>
       </c>
       <c r="E4" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -3917,7 +3917,7 @@
         <v>269</v>
       </c>
       <c r="E8" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -3935,7 +3935,7 @@
         <v>268</v>
       </c>
       <c r="E9" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -3953,7 +3953,7 @@
         <v>268</v>
       </c>
       <c r="E10" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -3971,7 +3971,7 @@
         <v>268</v>
       </c>
       <c r="E11" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -3989,7 +3989,7 @@
         <v>268</v>
       </c>
       <c r="E12" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>268</v>
       </c>
       <c r="E15" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -4063,7 +4063,7 @@
         <v>268</v>
       </c>
       <c r="E16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -4081,7 +4081,7 @@
         <v>268</v>
       </c>
       <c r="E17" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -4099,7 +4099,7 @@
         <v>268</v>
       </c>
       <c r="E18" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -4135,7 +4135,7 @@
         <v>268</v>
       </c>
       <c r="E20" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2"/>
     </row>
